--- a/heat_transfer/reactor_db.xlsx
+++ b/heat_transfer/reactor_db.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Reactors" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Filters" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -551,4 +552,140 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Tag No.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>面積(m2)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>F-101</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>加圧ろ過</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ラボスケール</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-102</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>加圧ろ過</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>パイロット</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-201</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>加圧ろ過</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>製造スケール</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>C-101</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>遠心ろ過</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>パイロット</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>C-201</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>遠心ろ過</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>製造スケール</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/heat_transfer/reactor_db.xlsx
+++ b/heat_transfer/reactor_db.xlsx
@@ -425,7 +425,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>U (W/m2K)</t>
+          <t>U (kJ/m2hK)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -451,7 +451,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>250</v>
+        <v>900</v>
       </c>
       <c r="C2" t="n">
         <v>50</v>
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>300</v>
+        <v>1080</v>
       </c>
       <c r="C3" t="n">
         <v>200</v>
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>200</v>
+        <v>720</v>
       </c>
       <c r="C4" t="n">
         <v>500</v>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>350</v>
+        <v>1260</v>
       </c>
       <c r="C5" t="n">
         <v>1000</v>
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>280</v>
+        <v>1008</v>
       </c>
       <c r="C6" t="n">
         <v>2000</v>

--- a/heat_transfer/reactor_db.xlsx
+++ b/heat_transfer/reactor_db.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -546,6 +546,27 @@
       <c r="E6" t="inlineStr">
         <is>
           <t>ED</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>R-106</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>900</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SD</t>
         </is>
       </c>
     </row>
